--- a/Level2_LowerBody_Day1_V1+V2_TEST.xlsx
+++ b/Level2_LowerBody_Day1_V1+V2_TEST.xlsx
@@ -457,10 +457,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="25.5" customHeight="1" s="13">
+    <row r="2" ht="30" customHeight="1" s="13">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Boss cycle: train inside the PRESCRIPTION range — 2 sets/skill so all tests fit one session. The top of the range is the TEST standard (✦); hitting it = signal to attempt the TEST. Pass = film, submit to Skool, unlock  ·  Every TEST = 2 sets to complete. On the attempt: 2 sets recommended, but hitting the standard once passes and advances.</t>
+          <t>Every test, one session. Warm up through the PRESCRIPTION (2 sets per test), then attempt the exact STANDARD — as many attempts as you need. Hit it once and it's passed ✦. Film that set and post it in Skool. Already passed a test on another Boss Test and posted it in Skool? It's done — no need to redo it. This Boss Test closes Version 1 and Version 2 of Day 1.</t>
         </is>
       </c>
     </row>
